--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-humanname.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-humanname.xlsx
@@ -350,7 +350,7 @@
     <t>nameRepresentationUse</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-EN-representation|5.3.0}
+    <t xml:space="preserve">Extension {iso21090-EN-representation|5.4.0}
 </t>
   </si>
   <si>
